--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T06:51:44+00:00</t>
+    <t>2026-06-25T12:51:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T12:51:02+00:00</t>
+    <t>2026-06-29T13:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-nutrition-consumption-frequency (DH1/DH3 numerische Codes), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
+    <t>Vollständige Antwortmöglichkeiten aus dem ATHIS Fragebogen (Österreichische Gesundheitsbefragung, STATISTIK AUSTRIA, Version 31.03.2025). Codes sind englisch; Display-Werte bleiben deutsch. Gruppiert nach Skalentypen. Hinweis: Bestehende PreNUDGE CodeSystems bleiben gültig – whoqol-bref-scale (LQ16-Zufriedenheitsskala), prenudge-alcoholuse-frequency (AL1 SNOMED-basiert).</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T13:58:40+00:00</t>
+    <t>2026-06-29T14:49:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-physical_activity/CodeSystem-athis-answers.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:49:16+00:00</t>
+    <t>2026-06-29T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
